--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6623" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6627" uniqueCount="664">
   <si>
     <t>League Name</t>
   </si>
@@ -2000,6 +2000,9 @@
     <t>The Ravana Bug Bowl</t>
   </si>
   <si>
+    <t>The Unemployment Bowl (Sponsored by Taco Bell)</t>
+  </si>
+  <si>
     <t>Award Name</t>
   </si>
   <si>
@@ -2251,8 +2254,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:F2" totalsRowShown="0">
-  <autoFilter ref="A1:F2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:F3" totalsRowShown="0">
+  <autoFilter ref="A1:F3"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Bowl Game"/>
     <tableColumn id="2" name="Player 1"/>
@@ -2596,7 +2599,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46244.97770779327</v>
+        <v>46244.99963512688</v>
       </c>
       <c r="C2">
         <v>226</v>
@@ -71749,7 +71752,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="24.7109375" customWidth="1"/>
@@ -71791,6 +71794,23 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
         <v>214</v>
       </c>
     </row>
@@ -71849,24 +71869,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>

--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6627" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6676" uniqueCount="668">
   <si>
     <t>League Name</t>
   </si>
@@ -2003,6 +2003,15 @@
     <t>The Unemployment Bowl (Sponsored by Taco Bell)</t>
   </si>
   <si>
+    <t>The Mixed Matthew Arts Bowl</t>
+  </si>
+  <si>
+    <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2663069370</t>
+  </si>
+  <si>
+    <t>Jumpluff</t>
+  </si>
+  <si>
     <t>Award Name</t>
   </si>
   <si>
@@ -2013,6 +2022,9 @@
   </si>
   <si>
     <t>TBD</t>
+  </si>
+  <si>
+    <t>Column8</t>
   </si>
 </sst>
 </file>
@@ -2254,8 +2266,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:F3" totalsRowShown="0">
-  <autoFilter ref="A1:F3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:F4" totalsRowShown="0">
+  <autoFilter ref="A1:F4"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Bowl Game"/>
     <tableColumn id="2" name="Player 1"/>
@@ -2269,7 +2281,24 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:C2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:H13" totalsRowShown="0">
+  <autoFilter ref="A1:H13"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Bowl Game"/>
+    <tableColumn id="2" name="Pokémon Trainer"/>
+    <tableColumn id="3" name="Pokémon Name"/>
+    <tableColumn id="4" name="Total Kills"/>
+    <tableColumn id="5" name="Direct Kills"/>
+    <tableColumn id="6" name="Passive Kills"/>
+    <tableColumn id="7" name="Deaths"/>
+    <tableColumn id="8" name="Column8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A1:C2" totalsRowShown="0">
   <autoFilter ref="A1:C2"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Award Name"/>
@@ -2599,7 +2628,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46244.99963512688</v>
+        <v>46245.74618281137</v>
       </c>
       <c r="C2">
         <v>226</v>
@@ -71752,7 +71781,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="24.7109375" customWidth="1"/>
@@ -71807,31 +71836,54 @@
       <c r="C3" t="s">
         <v>36</v>
       </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
       <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>660</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>214</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="24.7109375" customWidth="1"/>
     <col min="4" max="7" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>657</v>
       </c>
@@ -71853,9 +71905,291 @@
       <c r="G1" t="s">
         <v>288</v>
       </c>
+      <c r="H1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>513</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>659</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>422</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>659</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>460</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>659</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>659</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>382</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>659</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="s">
+        <v>419</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>659</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>488</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>659</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>566</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>659</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>296</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>659</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>299</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>659</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>451</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -71869,24 +72203,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C2" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>

--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6676" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6674" uniqueCount="668">
   <si>
     <t>League Name</t>
   </si>
@@ -2628,19 +2628,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46245.74618281137</v>
+        <v>46245.81005192214</v>
       </c>
       <c r="C2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>240</v>
       </c>
       <c r="F2" s="1">
-        <v>0.9416666666666667</v>
+        <v>0.9708333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -5855,9 +5855,6 @@
       <c r="E160">
         <v>0</v>
       </c>
-      <c r="F160" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161">
@@ -6663,9 +6660,6 @@
       <c r="E201">
         <v>0</v>
       </c>
-      <c r="F201" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202">
@@ -7034,11 +7028,11 @@
       <c r="C220" t="s">
         <v>32</v>
       </c>
+      <c r="D220" t="s">
+        <v>30</v>
+      </c>
       <c r="E220">
         <v>0</v>
-      </c>
-      <c r="F220" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -7382,11 +7376,11 @@
       <c r="C238" t="s">
         <v>50</v>
       </c>
+      <c r="D238" t="s">
+        <v>15</v>
+      </c>
       <c r="E238">
         <v>0</v>
-      </c>
-      <c r="F238" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -7399,11 +7393,11 @@
       <c r="C239" t="s">
         <v>30</v>
       </c>
+      <c r="D239" t="s">
+        <v>30</v>
+      </c>
       <c r="E239">
         <v>0</v>
-      </c>
-      <c r="F239" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -7416,14 +7410,14 @@
       <c r="C240" t="s">
         <v>34</v>
       </c>
+      <c r="D240" t="s">
+        <v>48</v>
+      </c>
       <c r="E240">
         <v>0</v>
       </c>
-      <c r="F240" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6">
+    </row>
+    <row r="241" spans="1:5">
       <c r="A241">
         <v>12</v>
       </c>
@@ -7433,11 +7427,11 @@
       <c r="C241" t="s">
         <v>53</v>
       </c>
+      <c r="D241" t="s">
+        <v>44</v>
+      </c>
       <c r="E241">
         <v>0</v>
-      </c>
-      <c r="F241" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -70238,13 +70232,13 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -70272,19 +70266,19 @@
         <v>650</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10">
-        <v>-18</v>
+        <v>-23</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -70292,19 +70286,19 @@
         <v>650</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>-26</v>
+        <v>-324</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -70455,16 +70449,16 @@
         <v>30</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -70478,13 +70472,13 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -70635,16 +70629,16 @@
         <v>15</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="F28">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -70695,16 +70689,16 @@
         <v>44</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31">
         <v>9</v>
       </c>
       <c r="E31">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -70798,13 +70792,13 @@
         <v>5</v>
       </c>
       <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
         <v>3</v>
       </c>
-      <c r="E36">
-        <v>6</v>
-      </c>
       <c r="F36">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -70818,13 +70812,13 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E37">
-        <v>-13</v>
+        <v>-19</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -70872,19 +70866,19 @@
         <v>653</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E40">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="F40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -70892,7 +70886,7 @@
         <v>653</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -70901,7 +70895,7 @@
         <v>9</v>
       </c>
       <c r="E41">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="F41">
         <v>10</v>
@@ -71102,13 +71096,13 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -71136,19 +71130,19 @@
         <v>650</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10">
-        <v>-18</v>
+        <v>-23</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -71156,19 +71150,19 @@
         <v>650</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>-26</v>
+        <v>-324</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -71319,16 +71313,16 @@
         <v>30</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -71342,13 +71336,13 @@
         <v>3</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -71499,16 +71493,16 @@
         <v>15</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="F28">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -71559,16 +71553,16 @@
         <v>44</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31">
         <v>9</v>
       </c>
       <c r="E31">
-        <v>-22</v>
+        <v>-19</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -71662,13 +71656,13 @@
         <v>5</v>
       </c>
       <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
         <v>3</v>
       </c>
-      <c r="E36">
-        <v>6</v>
-      </c>
       <c r="F36">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -71682,13 +71676,13 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E37">
-        <v>-13</v>
+        <v>-19</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -71736,19 +71730,19 @@
         <v>653</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E40">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="F40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -71756,7 +71750,7 @@
         <v>653</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -71765,7 +71759,7 @@
         <v>9</v>
       </c>
       <c r="E41">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="F41">
         <v>10</v>

--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6688" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6713" uniqueCount="678">
   <si>
     <t>League Name</t>
   </si>
@@ -854,6 +854,9 @@
     <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2661485265</t>
   </si>
   <si>
+    <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2663462386</t>
+  </si>
+  <si>
     <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2655827298</t>
   </si>
   <si>
@@ -873,9 +876,6 @@
   </si>
   <si>
     <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2659966163</t>
-  </si>
-  <si>
-    <t>&lt;GAME DATA NOT AVAILABLE&gt;</t>
   </si>
   <si>
     <t>The match was not scheduled, so this game is counted as a loss for both players.</t>
@@ -2033,6 +2033,9 @@
     <t>The Mixed Matthew Arts Bowl</t>
   </si>
   <si>
+    <t>&lt;GAME DATA NOT AVAILABLE&gt;</t>
+  </si>
+  <si>
     <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2663069370</t>
   </si>
   <si>
@@ -2249,8 +2252,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:G2712" totalsRowShown="0">
-  <autoFilter ref="A1:G2712"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:G2724" totalsRowShown="0">
+  <autoFilter ref="A1:G2724"/>
   <tableColumns count="7">
     <tableColumn id="1" name="Round"/>
     <tableColumn id="2" name="Pokémon Trainer"/>
@@ -2657,19 +2660,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46245.82671052212</v>
+        <v>46245.83792647405</v>
       </c>
       <c r="C2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>240</v>
       </c>
       <c r="F2" s="1">
-        <v>0.9958333333333333</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7928,13 +7931,13 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C229" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D229" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E229">
         <v>3</v>
@@ -7951,16 +7954,16 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C230" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D230" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="E230">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>278</v>
@@ -7974,16 +7977,16 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C231" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D231" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E231">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>279</v>
@@ -7997,16 +8000,16 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C232" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D232" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E232">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>280</v>
@@ -8020,16 +8023,16 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C233" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D233" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E233">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>281</v>
@@ -8043,16 +8046,16 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C234" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D234" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E234">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>282</v>
@@ -8066,16 +8069,16 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C235" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D235" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>283</v>
@@ -8089,15 +8092,18 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C236" t="s">
-        <v>47</v>
+        <v>54</v>
+      </c>
+      <c r="D236" t="s">
+        <v>38</v>
       </c>
       <c r="E236">
-        <v>0</v>
-      </c>
-      <c r="F236" t="s">
+        <v>5</v>
+      </c>
+      <c r="F236" s="3" t="s">
         <v>284</v>
       </c>
       <c r="G236" t="b">
@@ -8452,17 +8458,18 @@
     <hyperlink ref="F233" r:id="rId224"/>
     <hyperlink ref="F234" r:id="rId225"/>
     <hyperlink ref="F235" r:id="rId226"/>
+    <hyperlink ref="F236" r:id="rId227"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId227"/>
+    <tablePart r:id="rId228"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2712"/>
+  <dimension ref="A1:G2724"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -68091,16 +68098,16 @@
         <v>12</v>
       </c>
       <c r="B2593" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C2593" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="D2593">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2593">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2593">
         <v>0</v>
@@ -68114,22 +68121,22 @@
         <v>12</v>
       </c>
       <c r="B2594" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C2594" t="s">
-        <v>516</v>
+        <v>367</v>
       </c>
       <c r="D2594">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2594">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2594">
         <v>0</v>
       </c>
       <c r="G2594">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2595" spans="1:7">
@@ -68137,22 +68144,22 @@
         <v>12</v>
       </c>
       <c r="B2595" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C2595" t="s">
-        <v>565</v>
+        <v>512</v>
       </c>
       <c r="D2595">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2595">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2595">
         <v>0</v>
       </c>
       <c r="G2595">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2596" spans="1:7">
@@ -68160,10 +68167,10 @@
         <v>12</v>
       </c>
       <c r="B2596" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C2596" t="s">
-        <v>313</v>
+        <v>562</v>
       </c>
       <c r="D2596">
         <v>0</v>
@@ -68175,7 +68182,7 @@
         <v>0</v>
       </c>
       <c r="G2596">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2597" spans="1:7">
@@ -68183,22 +68190,22 @@
         <v>12</v>
       </c>
       <c r="B2597" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C2597" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="D2597">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2597">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2597">
         <v>0</v>
       </c>
       <c r="G2597">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2598" spans="1:7">
@@ -68206,10 +68213,10 @@
         <v>12</v>
       </c>
       <c r="B2598" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C2598" t="s">
-        <v>392</v>
+        <v>370</v>
       </c>
       <c r="D2598">
         <v>1</v>
@@ -68229,16 +68236,16 @@
         <v>12</v>
       </c>
       <c r="B2599" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C2599" t="s">
-        <v>587</v>
+        <v>388</v>
       </c>
       <c r="D2599">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2599">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2599">
         <v>0</v>
@@ -68252,10 +68259,10 @@
         <v>12</v>
       </c>
       <c r="B2600" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C2600" t="s">
-        <v>395</v>
+        <v>516</v>
       </c>
       <c r="D2600">
         <v>0</v>
@@ -68267,7 +68274,7 @@
         <v>0</v>
       </c>
       <c r="G2600">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2601" spans="1:7">
@@ -68275,10 +68282,10 @@
         <v>12</v>
       </c>
       <c r="B2601" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C2601" t="s">
-        <v>518</v>
+        <v>565</v>
       </c>
       <c r="D2601">
         <v>2</v>
@@ -68298,22 +68305,22 @@
         <v>12</v>
       </c>
       <c r="B2602" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C2602" t="s">
-        <v>396</v>
+        <v>313</v>
       </c>
       <c r="D2602">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2602">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2602">
         <v>0</v>
       </c>
       <c r="G2602">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2603" spans="1:7">
@@ -68321,10 +68328,10 @@
         <v>12</v>
       </c>
       <c r="B2603" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C2603" t="s">
-        <v>588</v>
+        <v>391</v>
       </c>
       <c r="D2603">
         <v>1</v>
@@ -68336,7 +68343,7 @@
         <v>0</v>
       </c>
       <c r="G2603">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2604" spans="1:7">
@@ -68344,16 +68351,16 @@
         <v>12</v>
       </c>
       <c r="B2604" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C2604" t="s">
-        <v>437</v>
+        <v>392</v>
       </c>
       <c r="D2604">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2604">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2604">
         <v>0</v>
@@ -68367,22 +68374,22 @@
         <v>12</v>
       </c>
       <c r="B2605" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C2605" t="s">
-        <v>399</v>
+        <v>587</v>
       </c>
       <c r="D2605">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2605">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2605">
         <v>0</v>
       </c>
       <c r="G2605">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2606" spans="1:7">
@@ -68390,16 +68397,16 @@
         <v>12</v>
       </c>
       <c r="B2606" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C2606" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D2606">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2606">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2606">
         <v>0</v>
@@ -68413,10 +68420,10 @@
         <v>12</v>
       </c>
       <c r="B2607" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C2607" t="s">
-        <v>603</v>
+        <v>518</v>
       </c>
       <c r="D2607">
         <v>2</v>
@@ -68436,10 +68443,10 @@
         <v>12</v>
       </c>
       <c r="B2608" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C2608" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="D2608">
         <v>1</v>
@@ -68459,22 +68466,22 @@
         <v>12</v>
       </c>
       <c r="B2609" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C2609" t="s">
-        <v>380</v>
+        <v>588</v>
       </c>
       <c r="D2609">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2609">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2609">
         <v>0</v>
       </c>
       <c r="G2609">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2610" spans="1:7">
@@ -68482,10 +68489,10 @@
         <v>12</v>
       </c>
       <c r="B2610" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C2610" t="s">
-        <v>519</v>
+        <v>437</v>
       </c>
       <c r="D2610">
         <v>0</v>
@@ -68497,7 +68504,7 @@
         <v>0</v>
       </c>
       <c r="G2610">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2611" spans="1:7">
@@ -68505,10 +68512,10 @@
         <v>12</v>
       </c>
       <c r="B2611" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C2611" t="s">
-        <v>563</v>
+        <v>399</v>
       </c>
       <c r="D2611">
         <v>0</v>
@@ -68520,7 +68527,7 @@
         <v>0</v>
       </c>
       <c r="G2611">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2612" spans="1:7">
@@ -68528,16 +68535,16 @@
         <v>12</v>
       </c>
       <c r="B2612" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C2612" t="s">
-        <v>469</v>
+        <v>400</v>
       </c>
       <c r="D2612">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2612">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2612">
         <v>0</v>
@@ -68551,22 +68558,22 @@
         <v>12</v>
       </c>
       <c r="B2613" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C2613" t="s">
-        <v>562</v>
+        <v>603</v>
       </c>
       <c r="D2613">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2613">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2613">
         <v>0</v>
       </c>
       <c r="G2613">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2614" spans="1:7">
@@ -68574,16 +68581,16 @@
         <v>12</v>
       </c>
       <c r="B2614" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C2614" t="s">
-        <v>522</v>
+        <v>364</v>
       </c>
       <c r="D2614">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2614">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2614">
         <v>0</v>
@@ -68597,10 +68604,10 @@
         <v>12</v>
       </c>
       <c r="B2615" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C2615" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="D2615">
         <v>0</v>
@@ -68612,7 +68619,7 @@
         <v>0</v>
       </c>
       <c r="G2615">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2616" spans="1:7">
@@ -68620,10 +68627,10 @@
         <v>12</v>
       </c>
       <c r="B2616" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C2616" t="s">
-        <v>391</v>
+        <v>519</v>
       </c>
       <c r="D2616">
         <v>0</v>
@@ -68635,7 +68642,7 @@
         <v>0</v>
       </c>
       <c r="G2616">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2617" spans="1:7">
@@ -68643,16 +68650,16 @@
         <v>12</v>
       </c>
       <c r="B2617" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C2617" t="s">
-        <v>527</v>
+        <v>563</v>
       </c>
       <c r="D2617">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2617">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2617">
         <v>0</v>
@@ -68666,16 +68673,16 @@
         <v>12</v>
       </c>
       <c r="B2618" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C2618" t="s">
-        <v>418</v>
+        <v>469</v>
       </c>
       <c r="D2618">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2618">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2618">
         <v>0</v>
@@ -68689,10 +68696,10 @@
         <v>12</v>
       </c>
       <c r="B2619" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C2619" t="s">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="D2619">
         <v>0</v>
@@ -68712,10 +68719,10 @@
         <v>12</v>
       </c>
       <c r="B2620" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C2620" t="s">
-        <v>400</v>
+        <v>522</v>
       </c>
       <c r="D2620">
         <v>0</v>
@@ -68735,16 +68742,16 @@
         <v>12</v>
       </c>
       <c r="B2621" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C2621" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="D2621">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2621">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2621">
         <v>0</v>
@@ -68758,16 +68765,16 @@
         <v>12</v>
       </c>
       <c r="B2622" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C2622" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="D2622">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2622">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2622">
         <v>0</v>
@@ -68781,10 +68788,10 @@
         <v>12</v>
       </c>
       <c r="B2623" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2623" t="s">
-        <v>448</v>
+        <v>527</v>
       </c>
       <c r="D2623">
         <v>1</v>
@@ -68804,10 +68811,10 @@
         <v>12</v>
       </c>
       <c r="B2624" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2624" t="s">
-        <v>553</v>
+        <v>418</v>
       </c>
       <c r="D2624">
         <v>0</v>
@@ -68819,7 +68826,7 @@
         <v>0</v>
       </c>
       <c r="G2624">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2625" spans="1:7">
@@ -68827,10 +68834,10 @@
         <v>12</v>
       </c>
       <c r="B2625" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2625" t="s">
-        <v>422</v>
+        <v>521</v>
       </c>
       <c r="D2625">
         <v>0</v>
@@ -68850,10 +68857,10 @@
         <v>12</v>
       </c>
       <c r="B2626" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2626" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="D2626">
         <v>0</v>
@@ -68865,7 +68872,7 @@
         <v>0</v>
       </c>
       <c r="G2626">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2627" spans="1:7">
@@ -68873,22 +68880,22 @@
         <v>12</v>
       </c>
       <c r="B2627" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2627" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D2627">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2627">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2627">
         <v>0</v>
       </c>
       <c r="G2627">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2628" spans="1:7">
@@ -68896,22 +68903,22 @@
         <v>12</v>
       </c>
       <c r="B2628" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2628" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="D2628">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2628">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2628">
         <v>0</v>
       </c>
       <c r="G2628">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2629" spans="1:7">
@@ -68919,10 +68926,10 @@
         <v>12</v>
       </c>
       <c r="B2629" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C2629" t="s">
-        <v>523</v>
+        <v>448</v>
       </c>
       <c r="D2629">
         <v>1</v>
@@ -68942,10 +68949,10 @@
         <v>12</v>
       </c>
       <c r="B2630" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C2630" t="s">
-        <v>524</v>
+        <v>553</v>
       </c>
       <c r="D2630">
         <v>0</v>
@@ -68965,22 +68972,22 @@
         <v>12</v>
       </c>
       <c r="B2631" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C2631" t="s">
-        <v>300</v>
+        <v>422</v>
       </c>
       <c r="D2631">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2631">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2631">
         <v>0</v>
       </c>
       <c r="G2631">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2632" spans="1:7">
@@ -68988,10 +68995,10 @@
         <v>12</v>
       </c>
       <c r="B2632" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C2632" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D2632">
         <v>0</v>
@@ -69011,16 +69018,16 @@
         <v>12</v>
       </c>
       <c r="B2633" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C2633" t="s">
-        <v>635</v>
+        <v>425</v>
       </c>
       <c r="D2633">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E2633">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2633">
         <v>0</v>
@@ -69034,16 +69041,16 @@
         <v>12</v>
       </c>
       <c r="B2634" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C2634" t="s">
-        <v>361</v>
+        <v>427</v>
       </c>
       <c r="D2634">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2634">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2634">
         <v>0</v>
@@ -69057,16 +69064,16 @@
         <v>12</v>
       </c>
       <c r="B2635" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C2635" t="s">
-        <v>617</v>
+        <v>523</v>
       </c>
       <c r="D2635">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2635">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2635">
         <v>0</v>
@@ -69080,10 +69087,10 @@
         <v>12</v>
       </c>
       <c r="B2636" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C2636" t="s">
-        <v>429</v>
+        <v>524</v>
       </c>
       <c r="D2636">
         <v>0</v>
@@ -69095,7 +69102,7 @@
         <v>0</v>
       </c>
       <c r="G2636">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2637" spans="1:7">
@@ -69103,22 +69110,22 @@
         <v>12</v>
       </c>
       <c r="B2637" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C2637" t="s">
-        <v>430</v>
+        <v>300</v>
       </c>
       <c r="D2637">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2637">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2637">
         <v>0</v>
       </c>
       <c r="G2637">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2638" spans="1:7">
@@ -69126,10 +69133,10 @@
         <v>12</v>
       </c>
       <c r="B2638" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C2638" t="s">
-        <v>354</v>
+        <v>416</v>
       </c>
       <c r="D2638">
         <v>0</v>
@@ -69141,7 +69148,7 @@
         <v>0</v>
       </c>
       <c r="G2638">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2639" spans="1:7">
@@ -69149,10 +69156,10 @@
         <v>12</v>
       </c>
       <c r="B2639" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C2639" t="s">
-        <v>432</v>
+        <v>635</v>
       </c>
       <c r="D2639">
         <v>0</v>
@@ -69164,7 +69171,7 @@
         <v>0</v>
       </c>
       <c r="G2639">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2640" spans="1:7">
@@ -69172,22 +69179,22 @@
         <v>12</v>
       </c>
       <c r="B2640" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C2640" t="s">
-        <v>433</v>
+        <v>361</v>
       </c>
       <c r="D2640">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2640">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2640">
         <v>0</v>
       </c>
       <c r="G2640">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2641" spans="1:7">
@@ -69195,10 +69202,10 @@
         <v>12</v>
       </c>
       <c r="B2641" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C2641" t="s">
-        <v>531</v>
+        <v>617</v>
       </c>
       <c r="D2641">
         <v>0</v>
@@ -69210,7 +69217,7 @@
         <v>0</v>
       </c>
       <c r="G2641">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2642" spans="1:7">
@@ -69218,22 +69225,22 @@
         <v>12</v>
       </c>
       <c r="B2642" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C2642" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D2642">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2642">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2642">
         <v>0</v>
       </c>
       <c r="G2642">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2643" spans="1:7">
@@ -69241,10 +69248,10 @@
         <v>12</v>
       </c>
       <c r="B2643" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C2643" t="s">
-        <v>568</v>
+        <v>430</v>
       </c>
       <c r="D2643">
         <v>0</v>
@@ -69256,7 +69263,7 @@
         <v>0</v>
       </c>
       <c r="G2643">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2644" spans="1:7">
@@ -69264,10 +69271,10 @@
         <v>12</v>
       </c>
       <c r="B2644" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C2644" t="s">
-        <v>435</v>
+        <v>354</v>
       </c>
       <c r="D2644">
         <v>0</v>
@@ -69279,7 +69286,7 @@
         <v>0</v>
       </c>
       <c r="G2644">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2645" spans="1:7">
@@ -69287,22 +69294,22 @@
         <v>12</v>
       </c>
       <c r="B2645" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C2645" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D2645">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2645">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2645">
         <v>0</v>
       </c>
       <c r="G2645">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2646" spans="1:7">
@@ -69310,22 +69317,22 @@
         <v>12</v>
       </c>
       <c r="B2646" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C2646" t="s">
-        <v>355</v>
+        <v>433</v>
       </c>
       <c r="D2646">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2646">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2646">
         <v>0</v>
       </c>
       <c r="G2646">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2647" spans="1:7">
@@ -69333,22 +69340,22 @@
         <v>12</v>
       </c>
       <c r="B2647" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C2647" t="s">
-        <v>643</v>
+        <v>531</v>
       </c>
       <c r="D2647">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2647">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2647">
         <v>0</v>
       </c>
       <c r="G2647">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2648" spans="1:7">
@@ -69356,16 +69363,16 @@
         <v>12</v>
       </c>
       <c r="B2648" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C2648" t="s">
-        <v>490</v>
+        <v>434</v>
       </c>
       <c r="D2648">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2648">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2648">
         <v>0</v>
@@ -69379,16 +69386,16 @@
         <v>12</v>
       </c>
       <c r="B2649" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C2649" t="s">
-        <v>652</v>
+        <v>568</v>
       </c>
       <c r="D2649">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2649">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2649">
         <v>0</v>
@@ -69402,22 +69409,22 @@
         <v>12</v>
       </c>
       <c r="B2650" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C2650" t="s">
-        <v>644</v>
+        <v>435</v>
       </c>
       <c r="D2650">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2650">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2650">
         <v>0</v>
       </c>
       <c r="G2650">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2651" spans="1:7">
@@ -69425,16 +69432,16 @@
         <v>12</v>
       </c>
       <c r="B2651" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C2651" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="D2651">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2651">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2651">
         <v>0</v>
@@ -69448,22 +69455,22 @@
         <v>12</v>
       </c>
       <c r="B2652" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C2652" t="s">
-        <v>613</v>
+        <v>355</v>
       </c>
       <c r="D2652">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2652">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2652">
         <v>0</v>
       </c>
       <c r="G2652">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2653" spans="1:7">
@@ -69471,16 +69478,16 @@
         <v>12</v>
       </c>
       <c r="B2653" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C2653" t="s">
-        <v>319</v>
+        <v>643</v>
       </c>
       <c r="D2653">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2653">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2653">
         <v>0</v>
@@ -69494,10 +69501,10 @@
         <v>12</v>
       </c>
       <c r="B2654" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C2654" t="s">
-        <v>532</v>
+        <v>490</v>
       </c>
       <c r="D2654">
         <v>0</v>
@@ -69509,7 +69516,7 @@
         <v>0</v>
       </c>
       <c r="G2654">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2655" spans="1:7">
@@ -69517,22 +69524,22 @@
         <v>12</v>
       </c>
       <c r="B2655" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C2655" t="s">
-        <v>441</v>
+        <v>652</v>
       </c>
       <c r="D2655">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2655">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2655">
         <v>0</v>
       </c>
       <c r="G2655">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2656" spans="1:7">
@@ -69540,16 +69547,16 @@
         <v>12</v>
       </c>
       <c r="B2656" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C2656" t="s">
-        <v>442</v>
+        <v>644</v>
       </c>
       <c r="D2656">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2656">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2656">
         <v>0</v>
@@ -69563,10 +69570,10 @@
         <v>12</v>
       </c>
       <c r="B2657" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C2657" t="s">
-        <v>420</v>
+        <v>463</v>
       </c>
       <c r="D2657">
         <v>0</v>
@@ -69578,7 +69585,7 @@
         <v>0</v>
       </c>
       <c r="G2657">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2658" spans="1:7">
@@ -69586,10 +69593,10 @@
         <v>12</v>
       </c>
       <c r="B2658" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="C2658" t="s">
-        <v>443</v>
+        <v>613</v>
       </c>
       <c r="D2658">
         <v>0</v>
@@ -69609,22 +69616,22 @@
         <v>12</v>
       </c>
       <c r="B2659" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C2659" t="s">
-        <v>444</v>
+        <v>319</v>
       </c>
       <c r="D2659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2659">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2659">
         <v>0</v>
       </c>
       <c r="G2659">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2660" spans="1:7">
@@ -69632,22 +69639,22 @@
         <v>12</v>
       </c>
       <c r="B2660" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C2660" t="s">
-        <v>445</v>
+        <v>532</v>
       </c>
       <c r="D2660">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2660">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2660">
         <v>0</v>
       </c>
       <c r="G2660">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2661" spans="1:7">
@@ -69655,10 +69662,10 @@
         <v>12</v>
       </c>
       <c r="B2661" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C2661" t="s">
-        <v>318</v>
+        <v>441</v>
       </c>
       <c r="D2661">
         <v>0</v>
@@ -69678,22 +69685,22 @@
         <v>12</v>
       </c>
       <c r="B2662" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C2662" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="D2662">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2662">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2662">
         <v>0</v>
       </c>
       <c r="G2662">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2663" spans="1:7">
@@ -69701,10 +69708,10 @@
         <v>12</v>
       </c>
       <c r="B2663" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C2663" t="s">
-        <v>321</v>
+        <v>420</v>
       </c>
       <c r="D2663">
         <v>0</v>
@@ -69716,7 +69723,7 @@
         <v>0</v>
       </c>
       <c r="G2663">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2664" spans="1:7">
@@ -69724,16 +69731,16 @@
         <v>12</v>
       </c>
       <c r="B2664" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C2664" t="s">
-        <v>571</v>
+        <v>443</v>
       </c>
       <c r="D2664">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2664">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2664">
         <v>0</v>
@@ -69747,22 +69754,22 @@
         <v>12</v>
       </c>
       <c r="B2665" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C2665" t="s">
-        <v>384</v>
+        <v>444</v>
       </c>
       <c r="D2665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2665">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2665">
         <v>0</v>
       </c>
       <c r="G2665">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2666" spans="1:7">
@@ -69770,22 +69777,22 @@
         <v>12</v>
       </c>
       <c r="B2666" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C2666" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D2666">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2666">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2666">
         <v>0</v>
       </c>
       <c r="G2666">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2667" spans="1:7">
@@ -69793,10 +69800,10 @@
         <v>12</v>
       </c>
       <c r="B2667" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C2667" t="s">
-        <v>448</v>
+        <v>318</v>
       </c>
       <c r="D2667">
         <v>0</v>
@@ -69816,22 +69823,22 @@
         <v>12</v>
       </c>
       <c r="B2668" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C2668" t="s">
-        <v>590</v>
+        <v>446</v>
       </c>
       <c r="D2668">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2668">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2668">
         <v>0</v>
       </c>
       <c r="G2668">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2669" spans="1:7">
@@ -69839,10 +69846,10 @@
         <v>12</v>
       </c>
       <c r="B2669" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C2669" t="s">
-        <v>449</v>
+        <v>321</v>
       </c>
       <c r="D2669">
         <v>0</v>
@@ -69854,7 +69861,7 @@
         <v>0</v>
       </c>
       <c r="G2669">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2670" spans="1:7">
@@ -69862,16 +69869,16 @@
         <v>12</v>
       </c>
       <c r="B2670" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C2670" t="s">
-        <v>390</v>
+        <v>571</v>
       </c>
       <c r="D2670">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2670">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2670">
         <v>0</v>
@@ -69885,10 +69892,10 @@
         <v>12</v>
       </c>
       <c r="B2671" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C2671" t="s">
-        <v>328</v>
+        <v>384</v>
       </c>
       <c r="D2671">
         <v>0</v>
@@ -69908,10 +69915,10 @@
         <v>12</v>
       </c>
       <c r="B2672" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C2672" t="s">
-        <v>538</v>
+        <v>447</v>
       </c>
       <c r="D2672">
         <v>0</v>
@@ -69923,7 +69930,7 @@
         <v>0</v>
       </c>
       <c r="G2672">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2673" spans="1:7">
@@ -69931,22 +69938,22 @@
         <v>12</v>
       </c>
       <c r="B2673" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C2673" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="D2673">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2673">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2673">
         <v>0</v>
       </c>
       <c r="G2673">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2674" spans="1:7">
@@ -69954,16 +69961,16 @@
         <v>12</v>
       </c>
       <c r="B2674" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C2674" t="s">
-        <v>457</v>
+        <v>590</v>
       </c>
       <c r="D2674">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2674">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2674">
         <v>0</v>
@@ -69977,10 +69984,10 @@
         <v>12</v>
       </c>
       <c r="B2675" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C2675" t="s">
-        <v>539</v>
+        <v>449</v>
       </c>
       <c r="D2675">
         <v>0</v>
@@ -69992,7 +69999,7 @@
         <v>0</v>
       </c>
       <c r="G2675">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2676" spans="1:7">
@@ -70000,16 +70007,16 @@
         <v>12</v>
       </c>
       <c r="B2676" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C2676" t="s">
-        <v>333</v>
+        <v>390</v>
       </c>
       <c r="D2676">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2676">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2676">
         <v>0</v>
@@ -70023,10 +70030,10 @@
         <v>12</v>
       </c>
       <c r="B2677" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2677" t="s">
-        <v>460</v>
+        <v>328</v>
       </c>
       <c r="D2677">
         <v>0</v>
@@ -70038,7 +70045,7 @@
         <v>0</v>
       </c>
       <c r="G2677">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2678" spans="1:7">
@@ -70046,10 +70053,10 @@
         <v>12</v>
       </c>
       <c r="B2678" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2678" t="s">
-        <v>461</v>
+        <v>538</v>
       </c>
       <c r="D2678">
         <v>0</v>
@@ -70061,7 +70068,7 @@
         <v>0</v>
       </c>
       <c r="G2678">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2679" spans="1:7">
@@ -70069,16 +70076,16 @@
         <v>12</v>
       </c>
       <c r="B2679" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2679" t="s">
-        <v>345</v>
+        <v>456</v>
       </c>
       <c r="D2679">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2679">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2679">
         <v>0</v>
@@ -70092,16 +70099,16 @@
         <v>12</v>
       </c>
       <c r="B2680" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2680" t="s">
-        <v>377</v>
+        <v>457</v>
       </c>
       <c r="D2680">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2680">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2680">
         <v>0</v>
@@ -70115,10 +70122,10 @@
         <v>12</v>
       </c>
       <c r="B2681" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2681" t="s">
-        <v>581</v>
+        <v>539</v>
       </c>
       <c r="D2681">
         <v>0</v>
@@ -70138,10 +70145,10 @@
         <v>12</v>
       </c>
       <c r="B2682" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2682" t="s">
-        <v>505</v>
+        <v>333</v>
       </c>
       <c r="D2682">
         <v>2</v>
@@ -70161,10 +70168,10 @@
         <v>12</v>
       </c>
       <c r="B2683" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2683" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D2683">
         <v>0</v>
@@ -70176,7 +70183,7 @@
         <v>0</v>
       </c>
       <c r="G2683">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2684" spans="1:7">
@@ -70184,16 +70191,16 @@
         <v>12</v>
       </c>
       <c r="B2684" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2684" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D2684">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2684">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2684">
         <v>0</v>
@@ -70207,16 +70214,16 @@
         <v>12</v>
       </c>
       <c r="B2685" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2685" t="s">
-        <v>466</v>
+        <v>345</v>
       </c>
       <c r="D2685">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2685">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2685">
         <v>0</v>
@@ -70230,16 +70237,16 @@
         <v>12</v>
       </c>
       <c r="B2686" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2686" t="s">
-        <v>301</v>
+        <v>377</v>
       </c>
       <c r="D2686">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2686">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2686">
         <v>0</v>
@@ -70253,10 +70260,10 @@
         <v>12</v>
       </c>
       <c r="B2687" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2687" t="s">
-        <v>327</v>
+        <v>581</v>
       </c>
       <c r="D2687">
         <v>0</v>
@@ -70268,7 +70275,7 @@
         <v>0</v>
       </c>
       <c r="G2687">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2688" spans="1:7">
@@ -70276,16 +70283,16 @@
         <v>12</v>
       </c>
       <c r="B2688" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2688" t="s">
-        <v>392</v>
+        <v>505</v>
       </c>
       <c r="D2688">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2688">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2688">
         <v>0</v>
@@ -70299,10 +70306,10 @@
         <v>12</v>
       </c>
       <c r="B2689" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C2689" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D2689">
         <v>0</v>
@@ -70322,16 +70329,16 @@
         <v>12</v>
       </c>
       <c r="B2690" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C2690" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D2690">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2690">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2690">
         <v>0</v>
@@ -70345,22 +70352,22 @@
         <v>12</v>
       </c>
       <c r="B2691" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C2691" t="s">
-        <v>317</v>
+        <v>466</v>
       </c>
       <c r="D2691">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2691">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2691">
         <v>0</v>
       </c>
       <c r="G2691">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2692" spans="1:7">
@@ -70368,16 +70375,16 @@
         <v>12</v>
       </c>
       <c r="B2692" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C2692" t="s">
-        <v>546</v>
+        <v>301</v>
       </c>
       <c r="D2692">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2692">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2692">
         <v>0</v>
@@ -70391,16 +70398,16 @@
         <v>12</v>
       </c>
       <c r="B2693" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C2693" t="s">
-        <v>416</v>
+        <v>327</v>
       </c>
       <c r="D2693">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2693">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2693">
         <v>0</v>
@@ -70414,16 +70421,16 @@
         <v>12</v>
       </c>
       <c r="B2694" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C2694" t="s">
-        <v>543</v>
+        <v>392</v>
       </c>
       <c r="D2694">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2694">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2694">
         <v>0</v>
@@ -70437,16 +70444,16 @@
         <v>12</v>
       </c>
       <c r="B2695" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C2695" t="s">
-        <v>367</v>
+        <v>468</v>
       </c>
       <c r="D2695">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2695">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2695">
         <v>0</v>
@@ -70460,16 +70467,16 @@
         <v>12</v>
       </c>
       <c r="B2696" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C2696" t="s">
-        <v>546</v>
+        <v>469</v>
       </c>
       <c r="D2696">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2696">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2696">
         <v>0</v>
@@ -70483,10 +70490,10 @@
         <v>12</v>
       </c>
       <c r="B2697" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C2697" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="D2697">
         <v>0</v>
@@ -70506,16 +70513,16 @@
         <v>12</v>
       </c>
       <c r="B2698" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C2698" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D2698">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2698">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2698">
         <v>0</v>
@@ -70529,10 +70536,10 @@
         <v>12</v>
       </c>
       <c r="B2699" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C2699" t="s">
-        <v>338</v>
+        <v>416</v>
       </c>
       <c r="D2699">
         <v>1</v>
@@ -70552,16 +70559,16 @@
         <v>12</v>
       </c>
       <c r="B2700" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C2700" t="s">
-        <v>478</v>
+        <v>543</v>
       </c>
       <c r="D2700">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2700">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2700">
         <v>0</v>
@@ -70575,10 +70582,10 @@
         <v>12</v>
       </c>
       <c r="B2701" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C2701" t="s">
-        <v>487</v>
+        <v>388</v>
       </c>
       <c r="D2701">
         <v>1</v>
@@ -70590,7 +70597,7 @@
         <v>0</v>
       </c>
       <c r="G2701">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2702" spans="1:7">
@@ -70598,10 +70605,10 @@
         <v>12</v>
       </c>
       <c r="B2702" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C2702" t="s">
-        <v>311</v>
+        <v>471</v>
       </c>
       <c r="D2702">
         <v>0</v>
@@ -70621,22 +70628,22 @@
         <v>12</v>
       </c>
       <c r="B2703" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C2703" t="s">
-        <v>404</v>
+        <v>544</v>
       </c>
       <c r="D2703">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2703">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2703">
         <v>0</v>
       </c>
       <c r="G2703">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2704" spans="1:7">
@@ -70644,22 +70651,22 @@
         <v>12</v>
       </c>
       <c r="B2704" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C2704" t="s">
-        <v>553</v>
+        <v>324</v>
       </c>
       <c r="D2704">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2704">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2704">
         <v>0</v>
       </c>
       <c r="G2704">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2705" spans="1:7">
@@ -70667,10 +70674,10 @@
         <v>12</v>
       </c>
       <c r="B2705" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C2705" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="D2705">
         <v>0</v>
@@ -70690,10 +70697,10 @@
         <v>12</v>
       </c>
       <c r="B2706" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C2706" t="s">
-        <v>529</v>
+        <v>475</v>
       </c>
       <c r="D2706">
         <v>1</v>
@@ -70713,16 +70720,16 @@
         <v>12</v>
       </c>
       <c r="B2707" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C2707" t="s">
-        <v>595</v>
+        <v>367</v>
       </c>
       <c r="D2707">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2707">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2707">
         <v>0</v>
@@ -70736,16 +70743,16 @@
         <v>12</v>
       </c>
       <c r="B2708" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C2708" t="s">
-        <v>466</v>
+        <v>546</v>
       </c>
       <c r="D2708">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2708">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2708">
         <v>0</v>
@@ -70759,10 +70766,10 @@
         <v>12</v>
       </c>
       <c r="B2709" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C2709" t="s">
-        <v>641</v>
+        <v>325</v>
       </c>
       <c r="D2709">
         <v>0</v>
@@ -70782,10 +70789,10 @@
         <v>12</v>
       </c>
       <c r="B2710" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C2710" t="s">
-        <v>492</v>
+        <v>547</v>
       </c>
       <c r="D2710">
         <v>0</v>
@@ -70805,10 +70812,10 @@
         <v>12</v>
       </c>
       <c r="B2711" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C2711" t="s">
-        <v>554</v>
+        <v>338</v>
       </c>
       <c r="D2711">
         <v>1</v>
@@ -70828,21 +70835,297 @@
         <v>12</v>
       </c>
       <c r="B2712" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2712" t="s">
+        <v>478</v>
+      </c>
+      <c r="D2712">
+        <v>2</v>
+      </c>
+      <c r="E2712">
+        <v>2</v>
+      </c>
+      <c r="F2712">
+        <v>0</v>
+      </c>
+      <c r="G2712">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2713" spans="1:7">
+      <c r="A2713">
+        <v>12</v>
+      </c>
+      <c r="B2713" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2713" t="s">
+        <v>487</v>
+      </c>
+      <c r="D2713">
+        <v>1</v>
+      </c>
+      <c r="E2713">
+        <v>1</v>
+      </c>
+      <c r="F2713">
+        <v>0</v>
+      </c>
+      <c r="G2713">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2714" spans="1:7">
+      <c r="A2714">
+        <v>12</v>
+      </c>
+      <c r="B2714" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2714" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2714">
+        <v>0</v>
+      </c>
+      <c r="E2714">
+        <v>0</v>
+      </c>
+      <c r="F2714">
+        <v>0</v>
+      </c>
+      <c r="G2714">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2715" spans="1:7">
+      <c r="A2715">
+        <v>12</v>
+      </c>
+      <c r="B2715" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2715" t="s">
+        <v>404</v>
+      </c>
+      <c r="D2715">
+        <v>0</v>
+      </c>
+      <c r="E2715">
+        <v>0</v>
+      </c>
+      <c r="F2715">
+        <v>0</v>
+      </c>
+      <c r="G2715">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2716" spans="1:7">
+      <c r="A2716">
+        <v>12</v>
+      </c>
+      <c r="B2716" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2716" t="s">
+        <v>553</v>
+      </c>
+      <c r="D2716">
+        <v>0</v>
+      </c>
+      <c r="E2716">
+        <v>0</v>
+      </c>
+      <c r="F2716">
+        <v>0</v>
+      </c>
+      <c r="G2716">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2717" spans="1:7">
+      <c r="A2717">
+        <v>12</v>
+      </c>
+      <c r="B2717" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2717" t="s">
+        <v>488</v>
+      </c>
+      <c r="D2717">
+        <v>0</v>
+      </c>
+      <c r="E2717">
+        <v>0</v>
+      </c>
+      <c r="F2717">
+        <v>0</v>
+      </c>
+      <c r="G2717">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2718" spans="1:7">
+      <c r="A2718">
+        <v>12</v>
+      </c>
+      <c r="B2718" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2718" t="s">
+        <v>529</v>
+      </c>
+      <c r="D2718">
+        <v>1</v>
+      </c>
+      <c r="E2718">
+        <v>1</v>
+      </c>
+      <c r="F2718">
+        <v>0</v>
+      </c>
+      <c r="G2718">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2719" spans="1:7">
+      <c r="A2719">
+        <v>12</v>
+      </c>
+      <c r="B2719" t="s">
         <v>19</v>
       </c>
-      <c r="C2712" t="s">
+      <c r="C2719" t="s">
+        <v>595</v>
+      </c>
+      <c r="D2719">
+        <v>0</v>
+      </c>
+      <c r="E2719">
+        <v>0</v>
+      </c>
+      <c r="F2719">
+        <v>0</v>
+      </c>
+      <c r="G2719">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2720" spans="1:7">
+      <c r="A2720">
+        <v>12</v>
+      </c>
+      <c r="B2720" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2720" t="s">
+        <v>466</v>
+      </c>
+      <c r="D2720">
+        <v>0</v>
+      </c>
+      <c r="E2720">
+        <v>0</v>
+      </c>
+      <c r="F2720">
+        <v>0</v>
+      </c>
+      <c r="G2720">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:7">
+      <c r="A2721">
+        <v>12</v>
+      </c>
+      <c r="B2721" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2721" t="s">
+        <v>641</v>
+      </c>
+      <c r="D2721">
+        <v>0</v>
+      </c>
+      <c r="E2721">
+        <v>0</v>
+      </c>
+      <c r="F2721">
+        <v>0</v>
+      </c>
+      <c r="G2721">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2722" spans="1:7">
+      <c r="A2722">
+        <v>12</v>
+      </c>
+      <c r="B2722" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2722" t="s">
+        <v>492</v>
+      </c>
+      <c r="D2722">
+        <v>0</v>
+      </c>
+      <c r="E2722">
+        <v>0</v>
+      </c>
+      <c r="F2722">
+        <v>0</v>
+      </c>
+      <c r="G2722">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2723" spans="1:7">
+      <c r="A2723">
+        <v>12</v>
+      </c>
+      <c r="B2723" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2723" t="s">
+        <v>554</v>
+      </c>
+      <c r="D2723">
+        <v>1</v>
+      </c>
+      <c r="E2723">
+        <v>1</v>
+      </c>
+      <c r="F2723">
+        <v>0</v>
+      </c>
+      <c r="G2723">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2724" spans="1:7">
+      <c r="A2724">
+        <v>12</v>
+      </c>
+      <c r="B2724" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2724" t="s">
         <v>609</v>
       </c>
-      <c r="D2712">
-        <v>0</v>
-      </c>
-      <c r="E2712">
-        <v>0</v>
-      </c>
-      <c r="F2712">
-        <v>0</v>
-      </c>
-      <c r="G2712">
+      <c r="D2724">
+        <v>0</v>
+      </c>
+      <c r="E2724">
+        <v>0</v>
+      </c>
+      <c r="F2724">
+        <v>0</v>
+      </c>
+      <c r="G2724">
         <v>1</v>
       </c>
     </row>
@@ -71354,16 +71637,16 @@
         <v>42</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -71557,13 +71840,13 @@
         <v>6</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -72218,16 +72501,16 @@
         <v>42</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -72421,13 +72704,13 @@
         <v>6</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -72602,7 +72885,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>284</v>
+        <v>670</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -72622,7 +72905,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -72639,7 +72922,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>284</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -72685,7 +72968,7 @@
         <v>297</v>
       </c>
       <c r="H1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -72696,7 +72979,7 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -72982,24 +73265,24 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>

--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7833" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7785" uniqueCount="682">
   <si>
     <t>League Name</t>
   </si>
@@ -2036,6 +2036,9 @@
     <t>TBD</t>
   </si>
   <si>
+    <t>EMW</t>
+  </si>
+  <si>
     <t>&lt;GAME DATA NOT AVAILABLE&gt;</t>
   </si>
   <si>
@@ -2675,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46245.8599701247</v>
+        <v>46246.82711791321</v>
       </c>
       <c r="C2">
         <v>240</v>
@@ -2710,7 +2713,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B1" t="s">
         <v>292</v>
@@ -2731,18 +2734,18 @@
         <v>297</v>
       </c>
       <c r="H1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2759,7 +2762,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -2782,7 +2785,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
@@ -2805,7 +2808,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B5" t="s">
         <v>35</v>
@@ -2828,7 +2831,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B6" t="s">
         <v>35</v>
@@ -2851,7 +2854,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
@@ -2874,7 +2877,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2897,7 +2900,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
@@ -2920,7 +2923,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -2943,7 +2946,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -2966,7 +2969,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B12" t="s">
         <v>38</v>
@@ -2989,7 +2992,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
@@ -3028,18 +3031,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B2" t="s">
         <v>669</v>
@@ -87997,7 +88000,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -88040,7 +88043,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -88054,13 +88057,13 @@
         <v>669</v>
       </c>
       <c r="C3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -88080,7 +88083,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -88100,7 +88103,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -88120,7 +88123,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -88140,7 +88143,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -88160,7 +88163,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -88180,7 +88183,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -88200,7 +88203,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -88208,7 +88211,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
         <v>669</v>
@@ -88220,7 +88223,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -88228,7 +88231,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
         <v>669</v>
@@ -88240,7 +88243,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -88248,7 +88251,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
         <v>669</v>
@@ -88260,7 +88263,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -88268,7 +88271,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
         <v>669</v>
@@ -88280,7 +88283,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -88288,7 +88291,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B15" t="s">
         <v>669</v>
@@ -88300,7 +88303,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -88308,7 +88311,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
         <v>669</v>
@@ -88320,7 +88323,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -88328,7 +88331,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
         <v>669</v>
@@ -88340,329 +88343,9 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="B18" t="s">
-        <v>669</v>
-      </c>
-      <c r="C18" t="s">
-        <v>669</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" t="s">
-        <v>670</v>
-      </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>3</v>
-      </c>
-      <c r="B19" t="s">
-        <v>669</v>
-      </c>
-      <c r="C19" t="s">
-        <v>669</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" t="s">
-        <v>670</v>
-      </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>3</v>
-      </c>
-      <c r="B20" t="s">
-        <v>669</v>
-      </c>
-      <c r="C20" t="s">
-        <v>669</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="s">
-        <v>670</v>
-      </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>3</v>
-      </c>
-      <c r="B21" t="s">
-        <v>669</v>
-      </c>
-      <c r="C21" t="s">
-        <v>669</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" t="s">
-        <v>670</v>
-      </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
-        <v>669</v>
-      </c>
-      <c r="C22" t="s">
-        <v>669</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" t="s">
-        <v>670</v>
-      </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>669</v>
-      </c>
-      <c r="C23" t="s">
-        <v>669</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" t="s">
-        <v>670</v>
-      </c>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>669</v>
-      </c>
-      <c r="C24" t="s">
-        <v>669</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" t="s">
-        <v>670</v>
-      </c>
-      <c r="G24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>669</v>
-      </c>
-      <c r="C25" t="s">
-        <v>669</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" t="s">
-        <v>670</v>
-      </c>
-      <c r="G25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>3</v>
-      </c>
-      <c r="B26" t="s">
-        <v>669</v>
-      </c>
-      <c r="C26" t="s">
-        <v>669</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" t="s">
-        <v>670</v>
-      </c>
-      <c r="G26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
-        <v>669</v>
-      </c>
-      <c r="C27" t="s">
-        <v>669</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" t="s">
-        <v>670</v>
-      </c>
-      <c r="G27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>4</v>
-      </c>
-      <c r="B28" t="s">
-        <v>669</v>
-      </c>
-      <c r="C28" t="s">
-        <v>669</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28" t="s">
-        <v>670</v>
-      </c>
-      <c r="G28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>4</v>
-      </c>
-      <c r="B29" t="s">
-        <v>669</v>
-      </c>
-      <c r="C29" t="s">
-        <v>669</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="s">
-        <v>670</v>
-      </c>
-      <c r="G29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>669</v>
-      </c>
-      <c r="C30" t="s">
-        <v>669</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" t="s">
-        <v>670</v>
-      </c>
-      <c r="G30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>5</v>
-      </c>
-      <c r="B31" t="s">
-        <v>669</v>
-      </c>
-      <c r="C31" t="s">
-        <v>669</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31" t="s">
-        <v>670</v>
-      </c>
-      <c r="G31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>5</v>
-      </c>
-      <c r="B32" t="s">
-        <v>669</v>
-      </c>
-      <c r="C32" t="s">
-        <v>669</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32" t="s">
-        <v>670</v>
-      </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>6</v>
-      </c>
-      <c r="B33" t="s">
-        <v>669</v>
-      </c>
-      <c r="C33" t="s">
-        <v>669</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33" t="s">
-        <v>670</v>
-      </c>
-      <c r="G33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -88755,7 +88438,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -88775,7 +88458,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -88787,12 +88470,12 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -88807,12 +88490,12 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -88824,7 +88507,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>

--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7785" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7785" uniqueCount="681">
   <si>
     <t>League Name</t>
   </si>
@@ -2036,9 +2036,6 @@
     <t>TBD</t>
   </si>
   <si>
-    <t>EMW</t>
-  </si>
-  <si>
     <t>&lt;GAME DATA NOT AVAILABLE&gt;</t>
   </si>
   <si>
@@ -2678,7 +2675,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46246.82711791321</v>
+        <v>46246.83763993251</v>
       </c>
       <c r="C2">
         <v>240</v>
@@ -2713,7 +2710,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B1" t="s">
         <v>292</v>
@@ -2734,18 +2731,18 @@
         <v>297</v>
       </c>
       <c r="H1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2762,7 +2759,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -2785,7 +2782,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
@@ -2808,7 +2805,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B5" t="s">
         <v>35</v>
@@ -2831,7 +2828,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B6" t="s">
         <v>35</v>
@@ -2854,7 +2851,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
@@ -2877,7 +2874,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2900,7 +2897,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
@@ -2923,7 +2920,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -2946,7 +2943,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -2969,7 +2966,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B12" t="s">
         <v>38</v>
@@ -2992,7 +2989,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
@@ -3031,18 +3028,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B2" t="s">
         <v>669</v>
@@ -88043,7 +88040,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -88057,13 +88054,13 @@
         <v>669</v>
       </c>
       <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
         <v>670</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
-        <v>671</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -88074,16 +88071,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>669</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>669</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -88094,16 +88091,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>669</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>669</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -88114,16 +88111,16 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>669</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>669</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -88134,16 +88131,16 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>669</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>669</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -88154,16 +88151,16 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>669</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>669</v>
+        <v>49</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -88174,16 +88171,16 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>669</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>669</v>
+        <v>26</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -88194,16 +88191,16 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>669</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>669</v>
+        <v>44</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -88223,7 +88220,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -88243,7 +88240,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -88263,7 +88260,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -88283,7 +88280,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -88303,7 +88300,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -88323,7 +88320,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -88343,7 +88340,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
@@ -88438,7 +88435,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -88458,7 +88455,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -88470,12 +88467,12 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -88490,12 +88487,12 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -88507,7 +88504,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>

--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7785" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7834" uniqueCount="682">
   <si>
     <t>League Name</t>
   </si>
@@ -2039,6 +2039,9 @@
     <t>&lt;GAME DATA NOT AVAILABLE&gt;</t>
   </si>
   <si>
+    <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2665787938</t>
+  </si>
+  <si>
     <t>Bowl Game</t>
   </si>
   <si>
@@ -2675,7 +2678,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46246.83763993251</v>
+        <v>46251.56279202729</v>
       </c>
       <c r="C2">
         <v>240</v>
@@ -2710,7 +2713,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B1" t="s">
         <v>292</v>
@@ -2731,18 +2734,18 @@
         <v>297</v>
       </c>
       <c r="H1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2759,7 +2762,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -2782,7 +2785,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
@@ -2805,7 +2808,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B5" t="s">
         <v>35</v>
@@ -2828,7 +2831,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B6" t="s">
         <v>35</v>
@@ -2851,7 +2854,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
@@ -2874,7 +2877,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2897,7 +2900,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
@@ -2920,7 +2923,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -2943,7 +2946,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -2966,7 +2969,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B12" t="s">
         <v>38</v>
@@ -2989,7 +2992,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
@@ -3028,18 +3031,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B2" t="s">
         <v>669</v>
@@ -88051,16 +88054,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>669</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
       </c>
       <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
-        <v>670</v>
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>671</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -88071,10 +88077,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>669</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -88091,10 +88097,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -88111,10 +88117,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -88131,10 +88137,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -88151,10 +88157,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -88171,10 +88177,10 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -88271,7 +88277,7 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>669</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
         <v>669</v>
@@ -88347,13 +88353,16 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -88377,6 +88386,282 @@
       </c>
       <c r="G1" t="s">
         <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>565</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>557</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>628</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>2</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>435</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>436</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>437</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
+        <v>640</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -88386,7 +88671,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -88416,6 +88701,354 @@
       </c>
       <c r="I1" t="s">
         <v>668</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>557</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>628</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>434</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>435</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>436</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>437</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>640</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -88435,7 +89068,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -88455,7 +89088,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -88472,7 +89105,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -88487,12 +89120,12 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>

--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7834" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7871" uniqueCount="684">
   <si>
     <t>League Name</t>
   </si>
@@ -2057,7 +2057,13 @@
     <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2663069370</t>
   </si>
   <si>
+    <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2666449873</t>
+  </si>
+  <si>
     <t>Jumpluff</t>
+  </si>
+  <si>
+    <t>Togetic</t>
   </si>
   <si>
     <t>Award Name</t>
@@ -2331,8 +2337,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:H13" totalsRowShown="0">
-  <autoFilter ref="A1:H13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A1:H25" totalsRowShown="0">
+  <autoFilter ref="A1:H25"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Bowl Game"/>
     <tableColumn id="2" name="Pokémon Trainer"/>
@@ -2678,7 +2684,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46251.56279202729</v>
+        <v>46251.79949437737</v>
       </c>
       <c r="C2">
         <v>240</v>
@@ -2704,7 +2710,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="24.7109375" customWidth="1"/>
@@ -2734,7 +2740,7 @@
         <v>297</v>
       </c>
       <c r="H1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -2745,7 +2751,7 @@
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -3010,6 +3016,282 @@
         <v>0</v>
       </c>
       <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>675</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>643</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>675</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>463</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>675</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" t="s">
+        <v>613</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>675</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>490</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>675</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s">
+        <v>679</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>675</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>644</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>675</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>490</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>675</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" t="s">
+        <v>402</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>675</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>603</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>675</v>
+      </c>
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" t="s">
+        <v>380</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>675</v>
+      </c>
+      <c r="B24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>528</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>675</v>
+      </c>
+      <c r="B25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>520</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>1</v>
       </c>
     </row>
@@ -3031,18 +3313,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B2" t="s">
         <v>669</v>
@@ -89128,25 +89410,29 @@
         <v>675</v>
       </c>
       <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>57</v>
       </c>
       <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>670</v>
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>677</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1"/>
+    <hyperlink ref="F4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7871" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7920" uniqueCount="685">
   <si>
     <t>League Name</t>
   </si>
@@ -2039,6 +2039,9 @@
     <t>&lt;GAME DATA NOT AVAILABLE&gt;</t>
   </si>
   <si>
+    <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2666866025</t>
+  </si>
+  <si>
     <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2665787938</t>
   </si>
   <si>
@@ -2684,7 +2687,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46251.79949437737</v>
+        <v>46252.7557626292</v>
       </c>
       <c r="C2">
         <v>240</v>
@@ -2719,7 +2722,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B1" t="s">
         <v>292</v>
@@ -2740,18 +2743,18 @@
         <v>297</v>
       </c>
       <c r="H1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2768,7 +2771,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -2791,7 +2794,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
@@ -2814,7 +2817,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B5" t="s">
         <v>35</v>
@@ -2837,7 +2840,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B6" t="s">
         <v>35</v>
@@ -2860,7 +2863,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
@@ -2883,7 +2886,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2906,7 +2909,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
@@ -2929,7 +2932,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -2952,7 +2955,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -2975,7 +2978,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B12" t="s">
         <v>38</v>
@@ -2998,7 +3001,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
@@ -3021,7 +3024,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B14" t="s">
         <v>57</v>
@@ -3044,7 +3047,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B15" t="s">
         <v>57</v>
@@ -3067,7 +3070,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
@@ -3090,7 +3093,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B17" t="s">
         <v>57</v>
@@ -3113,13 +3116,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -3136,7 +3139,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B19" t="s">
         <v>57</v>
@@ -3159,7 +3162,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
@@ -3182,7 +3185,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
@@ -3205,7 +3208,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
@@ -3228,7 +3231,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
@@ -3251,7 +3254,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B24" t="s">
         <v>21</v>
@@ -3274,7 +3277,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B25" t="s">
         <v>21</v>
@@ -3313,18 +3316,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B2" t="s">
         <v>669</v>
@@ -88336,16 +88339,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>671</v>
@@ -88359,16 +88362,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>669</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
       </c>
       <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
-        <v>670</v>
+        <v>5</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>672</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -88379,10 +88385,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>669</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -88399,10 +88405,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -88419,10 +88425,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -88522,7 +88528,7 @@
         <v>669</v>
       </c>
       <c r="C12" t="s">
-        <v>669</v>
+        <v>51</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -88637,6 +88643,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1"/>
+    <hyperlink ref="F4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -88644,7 +88651,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -88675,10 +88682,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>388</v>
+        <v>301</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -88698,10 +88705,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>516</v>
+        <v>338</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -88721,10 +88728,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>372</v>
+        <v>599</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -88744,10 +88751,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>565</v>
+        <v>302</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -88767,16 +88774,16 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -88790,16 +88797,16 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>392</v>
+        <v>303</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -88813,10 +88820,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>628</v>
+        <v>388</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -88828,7 +88835,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -88836,22 +88843,22 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>434</v>
+        <v>516</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -88859,22 +88866,22 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -88882,22 +88889,22 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>436</v>
+        <v>565</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -88905,16 +88912,16 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>437</v>
+        <v>557</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -88928,21 +88935,297 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>524</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>300</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" t="s">
+        <v>389</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>387</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" t="s">
+        <v>416</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>635</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C20" t="s">
+        <v>628</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
+        <v>434</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
+        <v>435</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s">
+        <v>436</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>437</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" t="s">
         <v>640</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
         <v>0</v>
       </c>
     </row>
@@ -88953,7 +89236,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -88987,10 +89270,10 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>388</v>
+        <v>301</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -89016,10 +89299,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>516</v>
+        <v>338</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -89045,10 +89328,10 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>372</v>
+        <v>599</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -89074,10 +89357,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>565</v>
+        <v>302</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -89103,16 +89386,16 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -89124,7 +89407,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -89132,16 +89415,16 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>392</v>
+        <v>303</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -89153,7 +89436,7 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -89161,10 +89444,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>628</v>
+        <v>388</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -89176,7 +89459,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -89185,108 +89468,108 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>434</v>
+        <v>516</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>435</v>
+        <v>372</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>436</v>
+        <v>565</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>437</v>
+        <v>557</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -89298,7 +89581,7 @@
         <v>1</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -89306,30 +89589,378 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
+        <v>392</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>524</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>300</v>
+      </c>
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>389</v>
+      </c>
+      <c r="B16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>416</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>635</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>628</v>
+      </c>
+      <c r="B20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>434</v>
+      </c>
+      <c r="B21" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>435</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>436</v>
+      </c>
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>437</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
         <v>640</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>0</v>
       </c>
     </row>
@@ -89350,7 +89981,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -89370,7 +90001,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -89387,7 +90018,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -89402,12 +90033,12 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -89422,7 +90053,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>

--- a/parser/output/season 2.xlsx
+++ b/parser/output/season 2.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7920" uniqueCount="685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7969" uniqueCount="686">
   <si>
     <t>League Name</t>
   </si>
@@ -2039,6 +2039,9 @@
     <t>&lt;GAME DATA NOT AVAILABLE&gt;</t>
   </si>
   <si>
+    <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2667290204</t>
+  </si>
+  <si>
     <t>https://replay.pokemonshowdown.com/gen9natdexdraft-2666866025</t>
   </si>
   <si>
@@ -2687,7 +2690,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>46252.7557626292</v>
+        <v>46253.86807886782</v>
       </c>
       <c r="C2">
         <v>240</v>
@@ -2722,7 +2725,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B1" t="s">
         <v>292</v>
@@ -2743,18 +2746,18 @@
         <v>297</v>
       </c>
       <c r="H1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B2" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2771,7 +2774,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -2794,7 +2797,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
@@ -2817,7 +2820,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B5" t="s">
         <v>35</v>
@@ -2840,7 +2843,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B6" t="s">
         <v>35</v>
@@ -2863,7 +2866,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
@@ -2886,7 +2889,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B8" t="s">
         <v>38</v>
@@ -2909,7 +2912,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B9" t="s">
         <v>38</v>
@@ -2932,7 +2935,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
@@ -2955,7 +2958,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -2978,7 +2981,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B12" t="s">
         <v>38</v>
@@ -3001,7 +3004,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
@@ -3024,7 +3027,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B14" t="s">
         <v>57</v>
@@ -3047,7 +3050,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B15" t="s">
         <v>57</v>
@@ -3070,7 +3073,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B16" t="s">
         <v>57</v>
@@ -3093,7 +3096,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B17" t="s">
         <v>57</v>
@@ -3116,13 +3119,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B18" t="s">
         <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -3139,7 +3142,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B19" t="s">
         <v>57</v>
@@ -3162,7 +3165,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
@@ -3185,7 +3188,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B21" t="s">
         <v>21</v>
@@ -3208,7 +3211,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
@@ -3231,7 +3234,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
@@ -3254,7 +3257,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B24" t="s">
         <v>21</v>
@@ -3277,7 +3280,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B25" t="s">
         <v>21</v>
@@ -3316,18 +3319,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B2" t="s">
         <v>669</v>
@@ -88339,13 +88342,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -88362,16 +88365,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>672</v>
@@ -88385,16 +88388,19 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>669</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
       </c>
       <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>670</v>
+        <v>5</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>673</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -88405,10 +88411,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>669</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -88425,10 +88431,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -88525,7 +88531,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>669</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
@@ -88644,6 +88650,7 @@
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1"/>
     <hyperlink ref="F4" r:id="rId2"/>
+    <hyperlink ref="F5" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -88651,7 +88658,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -88958,22 +88965,22 @@
         <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>524</v>
+        <v>393</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -88981,10 +88988,10 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>300</v>
+        <v>394</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -88996,7 +89003,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -89004,19 +89011,19 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -89027,16 +89034,16 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>387</v>
+        <v>518</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -89050,10 +89057,10 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>416</v>
+        <v>588</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -89073,22 +89080,22 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>635</v>
+        <v>437</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -89096,16 +89103,16 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>628</v>
+        <v>524</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -89119,10 +89126,10 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
-        <v>434</v>
+        <v>300</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -89142,22 +89149,22 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s">
-        <v>435</v>
+        <v>389</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -89165,22 +89172,22 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>436</v>
+        <v>387</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -89188,16 +89195,16 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -89211,22 +89218,298 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>635</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26" t="s">
         <v>48</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
+        <v>628</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" t="s">
+        <v>434</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" t="s">
+        <v>435</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" t="s">
+        <v>436</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" t="s">
+        <v>437</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
         <v>640</v>
       </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>310</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>2</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" t="s">
+        <v>388</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>471</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>2</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" t="s">
+        <v>544</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>2</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" t="s">
+        <v>473</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>2</v>
+      </c>
+      <c r="B37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" t="s">
+        <v>474</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -89236,7 +89519,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -89618,39 +89901,39 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>524</v>
+        <v>393</v>
       </c>
       <c r="B14" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>300</v>
+        <v>394</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -89662,7 +89945,7 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -89671,24 +89954,24 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -89705,16 +89988,16 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>518</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -89726,7 +90009,7 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>1</v>
@@ -89734,10 +90017,10 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>416</v>
+        <v>588</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -89763,45 +90046,45 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>635</v>
+        <v>437</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>628</v>
+        <v>524</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -89813,7 +90096,7 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -89821,10 +90104,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>434</v>
+        <v>300</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -89850,74 +90133,74 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>435</v>
+        <v>389</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>436</v>
+        <v>387</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -89929,7 +90212,7 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>1</v>
@@ -89937,31 +90220,379 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
+        <v>635</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>628</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>434</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>435</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>436</v>
+      </c>
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>437</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
         <v>640</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B31" t="s">
         <v>48</v>
       </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>310</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>388</v>
+      </c>
+      <c r="B33" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>471</v>
+      </c>
+      <c r="B34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>544</v>
+      </c>
+      <c r="B35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>473</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>474</v>
+      </c>
+      <c r="B37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -89981,7 +90612,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
@@ -90001,7 +90632,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B2" t="s">
         <v>28</v>
@@ -90018,7 +90649,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -90033,12 +90664,12 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -90053,7 +90684,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
   </sheetData>
